--- a/CBT_2024_3회/산업안전기사_2024_3회_문항등록.xlsx
+++ b/CBT_2024_3회/산업안전기사_2024_3회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AG4" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;많은 지식과 경험을 주고받을 수 있는&lt;/strong&gt; 것이 Off JT 의 특징이다. &lt;strong&gt;여러 직장에서 모이기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 효과가 곧 나타난다 · 상호신뢰가 깊어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념 · 많은 사람을 한꺼번에 · 전문가 초빙 · 특별한 교재와 설비 · 여러 직장의 지식과 경험을 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 번에 많이 못 한다 · 상사의 능력에 좌우된다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현장에 바로 맞지 않을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;많은 지식과 경험을 주고받을 수 있는&lt;/strong&gt; 것이 Off JT의 특징이다. &lt;strong&gt;여러 직장에서 모이기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT (직장 안)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT (직장 밖)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속 상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직장 실정에 맞다 · 개개인에 맞춘다 · 효과가 곧 나타난다 · 상호신뢰가 깊어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;훈련에만 전념 · 많은 사람을 한꺼번에 · 전문가 초빙 · 특별한 교재와 설비 · 여러 직장의 지식과 경험을 교류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;단점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 번에 많이 못 한다 · 상사의 능력에 좌우된다&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;현장에 바로 맞지 않을 수 있다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH4" s="32" t="inlineStr">
         <is>
-          <t>② 교육 효과가 업무에 신속히 반영되는 것은 OJT 다.&lt;br&gt;③ 현장 관리감독자가 강사가 되는 것도 OJT 다.&lt;br&gt;④ 다수를 한꺼번에 교육하기 어려운 것은 OJT 의 단점이다.</t>
+          <t>② 교육 효과가 업무에 신속히 반영되는 것은 OJT다.&lt;br&gt;③ 현장 관리감독자가 강사가 되는 것도 OJT다.&lt;br&gt;④ 다수를 한꺼번에 교육하기 어려운 것은 OJT의 단점이다.</t>
         </is>
       </c>
       <c r="AI4" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「전념 · 많이 · 전문가 · 설비 · 교류」는 Off JT&lt;/strong&gt;, &lt;strong&gt;「맞춤 · 즉시 · 상사」는 OJT&lt;/strong&gt;다. 보기 ④는 &lt;strong&gt;OJT 의 단점을 Off JT 인 양 적어&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;교류할 수 있으면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「전념 · 많이 · 전문가 · 설비 · 교류」는 Off JT&lt;/strong&gt;, &lt;strong&gt;「맞춤 · 즉시 · 상사」는 OJT&lt;/strong&gt;다. 보기 ④는 &lt;strong&gt;OJT의 단점을 Off JT 인 양 적어&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;교류할 수 있으면 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1842,17 +1842,17 @@
       </c>
       <c r="AG6" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;직장 실정에 맞는 실제적 교육&lt;/strong&gt;은 OJT 의 장점이다.</t>
+          <t>&lt;strong&gt;직장 실정에 맞는 실제적 교육&lt;/strong&gt;은 OJT의 장점이다.</t>
         </is>
       </c>
       <c r="AH6" s="32" t="inlineStr">
         <is>
-          <t>① 우수한 전문가를 강사로 쓰는 것은 Off JT 의 장점이다.&lt;br&gt;② 특별 교재·교구·설비를 활용하는 것도 그렇다.&lt;br&gt;③ 다수에 대한 조직적 훈련도 그렇다.</t>
+          <t>① 우수한 전문가를 강사로 쓰는 것은 Off JT의 장점이다.&lt;br&gt;② 특별 교재·교구·설비를 활용하는 것도 그렇다.&lt;br&gt;③ 다수에 대한 조직적 훈련도 그렇다.</t>
         </is>
       </c>
       <c r="AI6" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;2번과 짝이다. &lt;strong&gt;「실정에 맞는」·「실제적인」&lt;/strong&gt;이라는 말이 붙으면 언제나 OJT 쪽이다. &lt;strong&gt;일터를 떠나면 그 일터의 사정에 꼭 맞출 수 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;실정에 맞으면 OJT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;2번과 짝이다. &lt;strong&gt;「실정에 맞는」·「실제적인」&lt;/strong&gt;이라는 말이 붙으면 언제나 OJT 쪽이다. &lt;strong&gt;일터를 떠나면 그 일터의 사정에 꼭 맞출 수 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;실정에 맞으면 OJT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AI7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;TBM(Tool Box Meeting)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「그 때 그 장소」&lt;/strong&gt;라는 말이 곧 TBM 이다. 도입 → 점검 정비 → 작업 지시 → 위험 예지 → 확인의 &lt;strong&gt;5단계&lt;/strong&gt;로 진행한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;그 자리에서 하면 TBM&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;TBM(Tool Box Meeting)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「그 때 그 장소」&lt;/strong&gt;라는 말이 곧 TBM이다. 도입 → 점검 정비 → 작업 지시 → 위험 예지 → 확인의 &lt;strong&gt;5단계&lt;/strong&gt;로 진행한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;그 자리에서 하면 TBM&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2100,17 +2100,17 @@
       </c>
       <c r="AG8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;7,000 [V] 이하&lt;/strong&gt;다. &lt;strong&gt;교류 7,000 [V] 에서 1분간 견디고 누설전류가 10 [mA] 이하&lt;/strong&gt; 라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;성능&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용도&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내충격성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물체의 낙하·비래&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내충격성 + 추락 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;낙하·비래 및 추락&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내충격성 + 내전압성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 및 감전&lt;/u&gt; · 7,000 [V] 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ABE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;셋 모두&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 · 추락 · 감전&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;7,000 [V] 이하&lt;/strong&gt;다. &lt;strong&gt;교류 7,000 [V]에서 1분간 견디고 누설전류가 10 [mA] 이하&lt;/strong&gt;라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;성능&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;용도&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내충격성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물체의 낙하·비래&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내충격성 + 추락 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;낙하·비래 및 추락&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내충격성 + 내전압성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 및 감전&lt;/u&gt; · 7,000 [V] 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ABE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;셋 모두&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낙하·비래 · 추락 · 감전&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
-          <t>① 750 [V] 는 옛 저압 직류의 경계값이다.&lt;br&gt;② 1,000 [V] 는 현행 저압 교류의 경계값이다.&lt;br&gt;③ 3,000 [V] 라는 기준은 없다.</t>
+          <t>① 750 [V]는 옛 저압 직류의 경계값이다.&lt;br&gt;② 1,000 [V]는 현행 저압 교류의 경계값이다.&lt;br&gt;③ 3,000 [V]라는 기준은 없다.</t>
         </is>
       </c>
       <c r="AI8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;보호구 안전인증 고시 — 안전모의 종류와 성능&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;A 는 충격(impact), B 는 추락(bump 방지), E 는 전기(electric)&lt;/strong&gt;로 새긴다. &lt;strong&gt;E 가 붙으면 7,000 [V]&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AE·ABE 는 7,000 [V]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;보호구 안전인증 고시 — 안전모의 종류와 성능&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;A는 충격(impact), B는 추락(bump 방지), E는 전기(electric)&lt;/strong&gt;로 새긴다. &lt;strong&gt;E가 붙으면 7,000 [V]&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AE·ABE는 7,000 [V]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AG15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;무(無)의 원칙&lt;/strong&gt;이다. &lt;strong&gt;「뿌리에서부터 제거」&lt;/strong&gt;라는 말이 곧 재해를 0 으로 만든다는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;무재해운동의 기본이념 3원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무(無)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠재위험요인을 뿌리째 없애 재해를 0 으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단순히 사고가 없는 상태가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선취(先取)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하기 전에 미리 찾아 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전제일의 원칙&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;참가(參加)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원이 함께 참여해 해결한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;참여의 원칙&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;무(無)의 원칙&lt;/strong&gt;이다. &lt;strong&gt;「뿌리에서부터 제거」&lt;/strong&gt;라는 말이 곧 재해를 0으로 만든다는 뜻이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;무재해운동의 기본이념 3원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무(無)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠재위험요인을 뿌리째 없애 재해를 0으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단순히 사고가 없는 상태가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선취(先取)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하기 전에 미리 찾아 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전제일의 원칙&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;참가(參加)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원이 함께 참여해 해결한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;참여의 원칙&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH15" s="32" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AH18" s="32" t="inlineStr">
         <is>
-          <t>② 99.9 [%] 라는 기준은 없다.&lt;br&gt;③ 99.5 [%] 도 없다.&lt;br&gt;④ 99.0 [%] 는 안면부 여과식 특급의 값이다.</t>
+          <t>② 99.9 [%]라는 기준은 없다.&lt;br&gt;③ 99.5 [%] 도 없다.&lt;br&gt;④ 99.0 [%]는 안면부 여과식 특급의 값이다.</t>
         </is>
       </c>
       <c r="AI18" s="32" t="inlineStr">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1 : 29 : 300&lt;/strong&gt;의 합이 330 이므로 660 은 &lt;strong&gt;2배&lt;/strong&gt;다. 경상은 $29 \times 2 = 58$ 명이다.&lt;img src="safe_A_2024_03_019_exp1.png"&gt;&lt;em&gt;하인리히의 1 : 29 : 300 — 아래로 갈수록 넓어진다&lt;/em&gt;</t>
+          <t>&lt;strong&gt;1 : 29 : 300&lt;/strong&gt;의 합이 330이므로 660은 &lt;strong&gt;2배&lt;/strong&gt;다. 경상은 $29 \times 2 = 58$ 명이다.&lt;img src="safe_A_2024_03_019_exp1.png"&gt;&lt;em&gt;하인리히의 1 : 29 : 300 — 아래로 갈수록 넓어진다&lt;/em&gt;</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AI21" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하인리히의 재해구성비율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;먼저 합(330)으로 나누어 배수를 구한 뒤&lt;/strong&gt; 각 항에 곱한다. 660 ÷ 330 = 2 이므로 &lt;strong&gt;중상 2 · 경상 58 · 무상해 600&lt;/strong&gt;이다. 세 값을 더하면 660 이 되어 검산된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1 : 29 : 300, 합은 330&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하인리히의 재해구성비율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;먼저 합(330)으로 나누어 배수를 구한 뒤&lt;/strong&gt; 각 항에 곱한다. 660 ÷ 330 = 2이므로 &lt;strong&gt;중상 2 · 경상 58 · 무상해 600&lt;/strong&gt;이다. 세 값을 더하면 660이 되어 검산된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1 : 29 : 300, 합은 330&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AI22" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재해통계의 목적&lt;/strong&gt;&lt;br&gt;19번의 재해조사와 같은 결이다. &lt;strong&gt;책임을 묻기 시작하면 통계가 감춰진다&lt;/strong&gt;. 통계의 목적은 &lt;strong&gt;설비 · 행동 · 관리를 고치는 것&lt;/strong&gt; 뿐이다. &lt;strong&gt;「인책」·「문책」&lt;/strong&gt;이 나오면 대개 답이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;문책 자료가 아니다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;재해통계의 목적&lt;/strong&gt;&lt;br&gt;19번의 재해조사와 같은 결이다. &lt;strong&gt;책임을 묻기 시작하면 통계가 감춰진다&lt;/strong&gt;. 통계의 목적은 &lt;strong&gt;설비 · 행동 · 관리를 고치는 것&lt;/strong&gt;뿐이다. &lt;strong&gt;「인책」·「문책」&lt;/strong&gt;이 나오면 대개 답이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;문책 자료가 아니다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4168,17 +4168,17 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;S 는 Standard 가 아니라 Simplify(단순화)&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업 개선의 ECRS&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영문&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;우리말&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Eliminate&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제거&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;없앨 수 없는가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Combine&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;합칠 수 없는가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Rearrange&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재배열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서를 바꿀 수 없는가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Simplify&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단순화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 간단히 할 수 없는가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;S는 Standard가 아니라 Simplify(단순화)&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업 개선의 ECRS&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;영문&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;우리말&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇을 하나&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Eliminate&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제거&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;없앨 수 없는가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Combine&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;합칠 수 없는가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Rearrange&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재배열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순서를 바꿀 수 없는가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Simplify&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단순화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 간단히 할 수 없는가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>① Combine(결합)은 ECRS 에 든다.&lt;br&gt;③ Eliminate(제거)도 그렇다.&lt;br&gt;④ Rearrange(재배열)도 그렇다.</t>
+          <t>① Combine(결합)은 ECRS에 든다.&lt;br&gt;③ Eliminate(제거)도 그렇다.&lt;br&gt;④ Rearrange(재배열)도 그렇다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;작업 개선의 원칙 ECRS&lt;/strong&gt;&lt;br&gt;네 물음을 &lt;strong&gt;「없애고 · 합치고 · 바꾸고 · 줄인다」&lt;/strong&gt; 순으로 던진다. &lt;strong&gt;없애는 것이 가장 확실한 개선&lt;/strong&gt;이라 E 가 맨 앞에 온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;S 는 Simplify&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;작업 개선의 원칙 ECRS&lt;/strong&gt;&lt;br&gt;네 물음을 &lt;strong&gt;「없애고 · 합치고 · 바꾸고 · 줄인다」&lt;/strong&gt; 순으로 던진다. &lt;strong&gt;없애는 것이 가장 확실한 개선&lt;/strong&gt;이라 E가 맨 앞에 온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;S는 Simplify&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="AG26" s="32" t="inlineStr">
         <is>
-          <t>$R ( t ) = e^{-t / 100}$ 이다. $A = e^{-50 / 100} = e^{-0.5} \fallingdotseq 0.607$, $B = e^{-100 / 100} = e^{-1} \fallingdotseq 0.368$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지수분포의 무기억성&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물음&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계산&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;새것이 50시간 견딜 확률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$e^{-50 / 100}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.607&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;새것이 100시간 견딜 확률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$e^{-100 / 100}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.368&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;100시간 쓴 것이 100시간 더 견딜 확률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$e^{-100 / 100}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.368&lt;/u&gt; — 새것과 같다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$R ( t ) = e^{-t / 100}$이다. $A = e^{-50 / 100} = e^{-0.5} \fallingdotseq 0.607$, $B = e^{-100 / 100} = e^{-1} \fallingdotseq 0.368$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지수분포의 무기억성&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물음&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;계산&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;새것이 50시간 견딜 확률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$e^{-50 / 100}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.607&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;새것이 100시간 견딜 확률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$e^{-100 / 100}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.368&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;100시간 쓴 것이 100시간 더 견딜 확률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$e^{-100 / 100}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.368&lt;/u&gt; — 새것과 같다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH26" s="32" t="inlineStr">
         <is>
-          <t>① A 는 0.368 이 아니라 0.607 이다.&lt;br&gt;③ A 와 B 가 서로 바뀌었다.&lt;br&gt;④ B 는 0.607 이 아니라 0.368 이다.</t>
+          <t>① A는 0.368이 아니라 0.607이다.&lt;br&gt;③ A와 B가 서로 바뀌었다.&lt;br&gt;④ B는 0.607이 아니라 0.368이다.</t>
         </is>
       </c>
       <c r="AI26" s="32" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="AG28" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최대근력의 15 [%] 이하&lt;/strong&gt; 라야 오래 버틸 수 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;최대근력과 유지 시간&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;힘의 크기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;버틸 수 있는 시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대근력의 100 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수 초&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;15 [%] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상당히 오래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;최대근력의 15 [%] 이하&lt;/strong&gt;라야 오래 버틸 수 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;최대근력과 유지 시간&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;힘의 크기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;버틸 수 있는 시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대근력의 100 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수 초&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 [%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;약 1분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;15 [%] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상당히 오래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH28" s="32" t="inlineStr">
         <is>
-          <t>② 20 [%] 는 기준보다 크다.&lt;br&gt;③ 25 [%] 도 그렇다.&lt;br&gt;④ 30 [%] 도 그렇다.</t>
+          <t>② 20 [%]는 기준보다 크다.&lt;br&gt;③ 25 [%] 도 그렇다.&lt;br&gt;④ 30 [%] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI28" s="32" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AI29" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;2점 문턱값(two-point threshold)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;두 점을 두 점으로 느끼는 최소 거리&lt;/strong&gt;다. &lt;strong&gt;작을수록 촘촘히 구별하니 예민&lt;/strong&gt; 하다. 손가락 끝이 가장 예민하기에 &lt;strong&gt;점자를 손끝으로 읽는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작을수록 예민 — 손끝이 가장 작다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;2점 문턱값(two-point threshold)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;두 점을 두 점으로 느끼는 최소 거리&lt;/strong&gt;다. &lt;strong&gt;작을수록 촘촘히 구별하니 예민&lt;/strong&gt;하다. 손가락 끝이 가장 예민하기에 &lt;strong&gt;점자를 손끝으로 읽는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작을수록 예민 — 손끝이 가장 작다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4918,17 +4918,17 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;구상단계(concept)&lt;/strong&gt;다. &lt;strong&gt;가장 이른 단계에서 위험을 정성적으로 훑는&lt;/strong&gt; 것이 PHA 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시스템 수명주기 5단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구상단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;PHA&lt;/u&gt; · 시스템 안전 목표 설정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정의(사양결정)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전성 부문의 사양 결정 · SSPP 작성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개발단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FMEA · FTA 등 위험분석 · 시제품 시험&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생산단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;품질관리 · 공정 안전&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전(배치)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전점검 기준 · 사고 조사&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;구상단계(concept)&lt;/strong&gt;다. &lt;strong&gt;가장 이른 단계에서 위험을 정성적으로 훑는&lt;/strong&gt; 것이 PHA다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;시스템 수명주기 5단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;하는 일&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구상단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;PHA&lt;/u&gt; · 시스템 안전 목표 설정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정의(사양결정)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전성 부문의 사양 결정 · SSPP 작성&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;개발단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FMEA · FTA 등 위험분석 · 시제품 시험&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생산단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;품질관리 · 공정 안전&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;운전(배치)단계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전점검 기준 · 사고 조사&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>② 정의단계는 안전 사양을 정하고 SSPP 를 작성하는 단계다.&lt;br&gt;③ 개발단계는 FMEA·FTA 등으로 자세히 분석하는 단계다.&lt;br&gt;④ 생산단계는 품질관리와 공정 안전을 다룬다.</t>
+          <t>② 정의단계는 안전 사양을 정하고 SSPP를 작성하는 단계다.&lt;br&gt;③ 개발단계는 FMEA·FTA 등으로 자세히 분석하는 단계다.&lt;br&gt;④ 생산단계는 품질관리와 공정 안전을 다룬다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시스템 수명주기와 PHA&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PHA 의 P 가 Preliminary(예비)&lt;/strong&gt;다. &lt;strong&gt;아직 설계도 없는 구상 단계에서 「무엇이 위험할까」를 먼저 훑는&lt;/strong&gt; 것이라 가장 앞에 온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;PHA 는 구상단계&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;시스템 수명주기와 PHA&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;PHA의 P가 Preliminary(예비)&lt;/strong&gt;다. &lt;strong&gt;아직 설계도 없는 구상 단계에서 「무엇이 위험할까」를 먼저 훑는&lt;/strong&gt; 것이라 가장 앞에 온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;PHA는 구상단계&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5305,17 +5305,17 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>$R = 1 - ( 1 - 0.7 ) ( 1 - 0.7 ) = 1 - 0.3 \times 0.3 = 1 - 0.09 = 0.91$ 이다.</t>
+          <t>$R = 1 - ( 1 - 0.7 ) ( 1 - 0.7 ) = 1 - 0.3 \times 0.3 = 1 - 0.09 = 0.91$이다.</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① 0.30 은 한 요소가 고장 날 확률이다.&lt;br&gt;② 0.49 는 직렬로 계산한 값($0.7 \times 0.7$)이다.&lt;br&gt;③ 0.70 은 한 요소의 신뢰도 그대로다.</t>
+          <t>① 0.30은 한 요소가 고장 날 확률이다.&lt;br&gt;② 0.49는 직렬로 계산한 값($0.7 \times 0.7$)이다.&lt;br&gt;③ 0.70은 한 요소의 신뢰도 그대로다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;병렬 결합의 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;병렬은 두 요소가 모두 고장 나야 시스템이 멈춘다&lt;/strong&gt;. 그래서 &lt;strong&gt;「둘 다 고장 날 확률(0.09)」을 1 에서 뺀다&lt;/strong&gt;. &lt;strong&gt;병렬은 늘 개별 요소보다 신뢰도가 높다(0.91 &amp;gt; 0.7)&lt;/strong&gt;는 것으로 검산된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $R = 1 - ( 1 - R_{1} ) ( 1 - R_{2} )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;병렬 결합의 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;병렬은 두 요소가 모두 고장 나야 시스템이 멈춘다&lt;/strong&gt;. 그래서 &lt;strong&gt;「둘 다 고장 날 확률(0.09)」을 1에서 뺀다&lt;/strong&gt;. &lt;strong&gt;병렬은 늘 개별 요소보다 신뢰도가 높다(0.91 &amp;gt; 0.7)&lt;/strong&gt;는 것으로 검산된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $R = 1 - ( 1 - R_{1} ) ( 1 - R_{2} )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5692,17 +5692,17 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>$WD = 0.85 W + 0.15 D = 0.85 \times 35 + 0.15 \times 30 = 29.75 + 4.5 = 34.25$ [℃] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;온열지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥스포드 지수 WD&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.85 \times \text{습구} + 0.15 \times \text{건구}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;습구에 0.85&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;실내 WBGT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.7 \times \text{자연습구} + 0.3 \times \text{흑구}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외 WBGT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.7 \times \text{자연습구} + 0.2 \times \text{흑구} + 0.1 \times \text{건구}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$WD = 0.85 W + 0.15 D = 0.85 \times 35 + 0.15 \times 30 = 29.75 + 4.5 = 34.25$ [℃]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;온열지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥스포드 지수 WD&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.85 \times \text{습구} + 0.15 \times \text{건구}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;습구에 0.85&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;실내 WBGT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.7 \times \text{자연습구} + 0.3 \times \text{흑구}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외 WBGT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.7 \times \text{자연습구} + 0.2 \times \text{흑구} + 0.1 \times \text{건구}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>① 27.75 [℃] 는 계수를 뒤바꾼 값에 가깝다.&lt;br&gt;② 24.58 [℃] 는 계산과 맞지 않는다.&lt;br&gt;③ 32.78 [℃] 도 맞지 않는다.</t>
+          <t>① 27.75 [℃]는 계수를 뒤바꾼 값에 가깝다.&lt;br&gt;② 24.58 [℃]는 계산과 맞지 않는다.&lt;br&gt;③ 32.78 [℃] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;옥스포드 지수(습건지수)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;습구에 0.85, 건구에 0.15&lt;/strong&gt;다. &lt;strong&gt;사람은 땀이 마르며 열을 버리므로 습도(습구온도)가 훨씬 중요&lt;/strong&gt; 하다 — 그래서 습구 쪽 계수가 크다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습구 0.85, 건구 0.15&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;옥스포드 지수(습건지수)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;습구에 0.85, 건구에 0.15&lt;/strong&gt;다. &lt;strong&gt;사람은 땀이 마르며 열을 버리므로 습도(습구온도)가 훨씬 중요&lt;/strong&gt;하다 — 그래서 습구 쪽 계수가 크다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습구 0.85, 건구 0.15&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5787,7 +5787,7 @@
       </c>
       <c r="U37" s="32" t="inlineStr">
         <is>
-          <t>실내에서 사용하는 습구흑구온도(WBGT: Wet Bulb Globe Temperature) 지수는? (단, NWB 는 자연습구, GT 는 흑구온도, DB 는 건구온도이다.)</t>
+          <t>실내에서 사용하는 습구흑구온도(WBGT: Wet Bulb Globe Temperature) 지수는? (단, NWB는 자연습구, GT는 흑구온도, DB는 건구온도이다.)</t>
         </is>
       </c>
       <c r="V37" s="32" t="inlineStr"/>
@@ -5821,17 +5821,17 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>실내(태양광선이 없는 곳)는 $\mathrm{WBGT} = 0.7 \mathrm{NWB} + 0.3 GT$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;WBGT 의 두 식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;실내 · 옥외(태양광선 없음)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.7 \mathrm{NWB} + 0.3 GT$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외(태양광선 있음)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.7 \mathrm{NWB} + 0.2 GT + 0.1 DB$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;세 항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>실내(태양광선이 없는 곳)는 $\mathrm{WBGT} = 0.7 \mathrm{NWB} + 0.3 GT$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;WBGT의 두 식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;실내 · 옥외(태양광선 없음)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.7 \mathrm{NWB} + 0.3 GT$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥외(태양광선 있음)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.7 \mathrm{NWB} + 0.2 GT + 0.1 DB$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;세 항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① 0.6 · 0.4 라는 계수는 없다.&lt;br&gt;③ 0.6 · 0.3 · 0.1 도 없다.&lt;br&gt;④ 0.7 · 0.2 · 0.1 은 옥외(태양광선 있음)의 식이다.</t>
+          <t>① 0.6 · 0.4라는 계수는 없다.&lt;br&gt;③ 0.6 · 0.3 · 0.1 도 없다.&lt;br&gt;④ 0.7 · 0.2 · 0.1은 옥외(태양광선 있음)의 식이다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;습구흑구온도지수(WBGT)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;자연습구의 계수 0.7 은 어느 쪽이든 같다&lt;/strong&gt;. &lt;strong&gt;실내는 두 항, 옥외는 세 항&lt;/strong&gt;이라는 것만 갈린다. 34번의 옥스포드 지수와 함께 &lt;strong&gt;습도 쪽 계수가 가장 크다&lt;/strong&gt;는 점이 공통이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;실내는 0.7 + 0.3, 옥외는 0.7 + 0.2 + 0.1&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;습구흑구온도지수(WBGT)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;자연습구의 계수 0.7은 어느 쪽이든 같다&lt;/strong&gt;. &lt;strong&gt;실내는 두 항, 옥외는 세 항&lt;/strong&gt;이라는 것만 갈린다. 34번의 옥스포드 지수와 함께 &lt;strong&gt;습도 쪽 계수가 가장 크다&lt;/strong&gt;는 점이 공통이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;실내는 0.7 + 0.3, 옥외는 0.7 + 0.2 + 0.1&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;140 [dB(A)]&lt;/strong&gt;다. 1일 100회면 이 값을 넘어서는 안 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;충격소음 작업의 기준 (규칙 제512조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최대 음압수준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;1일 노출횟수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;120 [dB] 을 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1만 회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;130 [dB] 을 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1천 회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;140 [dB] 을 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1백 회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;140 [dB(A)]&lt;/strong&gt;다. 1일 100회면 이 값을 넘어서는 안 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;충격소음 작업의 기준 (규칙 제512조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최대 음압수준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;1일 노출횟수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;120 [dB]을 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1만 회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;130 [dB]을 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1천 회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;140 [dB]을 초과&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1백 회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
         <is>
-          <t>① 110 [dB] 은 기준에 없다.&lt;br&gt;② 120 [dB] 은 1만 회 기준이다.&lt;br&gt;③ 130 [dB] 은 1천 회 기준이다.</t>
+          <t>① 110 [dB]은 기준에 없다.&lt;br&gt;② 120 [dB]은 1만 회 기준이다.&lt;br&gt;③ 130 [dB]은 1천 회 기준이다.</t>
         </is>
       </c>
       <c r="AI38" s="32" t="inlineStr">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;표적이 작고 멀수록 오래 걸린다&lt;/strong&gt;. $MT = a + b \log_{2} ( \dfrac{2 A}{W} )$ 에서 $A$ 는 거리, $W$ 는 표적의 너비다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Fitts 의 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이동시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표적이 작을수록&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정확히 맞춰야 하니 조심스럽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;거리가 멀수록&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 많이 움직여야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난이도 지수 ID&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\log_{2} ( 2 A / W )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;거리에 비례, 너비에 반비례&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;표적이 작고 멀수록 오래 걸린다&lt;/strong&gt;. $MT = a + b \log_{2} ( \dfrac{2 A}{W} )$에서 $A$는 거리, $W$는 표적의 너비다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;Fitts의 법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이동시간&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;까닭&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;표적이 작을수록&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정확히 맞춰야 하니 조심스럽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;거리가 멀수록&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;길어진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 많이 움직여야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난이도 지수 ID&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\log_{2} ( 2 A / W )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;거리에 비례, 너비에 반비례&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Fitts 의 법칙&lt;/strong&gt;&lt;br&gt;상식과 같다 — &lt;strong&gt;멀고 작은 과녁일수록 맞히기 어렵고 오래 걸린다&lt;/strong&gt;. 그래서 &lt;strong&gt;자주 쓰는 버튼은 크고 가까이&lt;/strong&gt; 두어야 한다는 설계 지침이 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작고 멀수록 오래 걸린다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;Fitts의 법칙&lt;/strong&gt;&lt;br&gt;상식과 같다 — &lt;strong&gt;멀고 작은 과녁일수록 맞히기 어렵고 오래 걸린다&lt;/strong&gt;. 그래서 &lt;strong&gt;자주 쓰는 버튼은 크고 가까이&lt;/strong&gt; 두어야 한다는 설계 지침이 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작고 멀수록 오래 걸린다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6724,17 +6724,17 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>$V = \dfrac{\pi D N}{1 {,} 000}$ 에서 $N = \dfrac{1 {,} 000 V}{\pi D} = \dfrac{1 {,} 000 \times 250}{\pi \times 200} \fallingdotseq 398$ [rpm] 이다.</t>
+          <t>$V = \dfrac{\pi D N}{1 {,} 000}$에서 $N = \dfrac{1 {,} 000 V}{\pi D} = \dfrac{1 {,} 000 \times 250}{\pi \times 200} \fallingdotseq 398$ [rpm]이다.</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>② 433 [rpm] 은 계산과 맞지 않는다.&lt;br&gt;③ 489 [rpm] 도 맞지 않는다.&lt;br&gt;④ 552 [rpm] 도 맞지 않는다.</t>
+          <t>② 433 [rpm]은 계산과 맞지 않는다.&lt;br&gt;③ 489 [rpm] 도 맞지 않는다.&lt;br&gt;④ 552 [rpm] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;원주속도와 회전수&lt;/strong&gt;&lt;br&gt;$V = \dfrac{\pi D N}{1 {,} 000}$ 에서 $D$&lt;strong&gt; 는 [mm], &lt;/strong&gt;$V$&lt;strong&gt; 는 [m/min]&lt;/strong&gt;이다. &lt;strong&gt;20 [cm] 를 200 [mm] 로 바꾸는 것&lt;/strong&gt;을 놓치면 자릿수가 열 배 어긋난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $N = 1 {,} 000 V \div ( \pi D )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;원주속도와 회전수&lt;/strong&gt;&lt;br&gt;$V = \dfrac{\pi D N}{1 {,} 000}$에서 $D$&lt;strong&gt;는 [mm], &lt;/strong&gt;$V$&lt;strong&gt;는 [m/min]&lt;/strong&gt;이다. &lt;strong&gt;20 [cm]를 200 [mm]로 바꾸는 것&lt;/strong&gt;을 놓치면 자릿수가 열 배 어긋난다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $N = 1 {,} 000 V \div ( \pi D )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="AH46" s="32" t="inlineStr">
         <is>
-          <t>① 발생기실 개구부는 1 [m] 가 아니라 1.5 [m] 이상 떨어져야 한다.&lt;br&gt;② 가스집합장치로부터는 3 [m] 가 아니라 5 [m] 이내에서 화기 사용을 금한다.&lt;br&gt;③ 흡연 금지 거리는 발생기에서 5 [m], 발생기실에서 3 [m] 이내다.</t>
+          <t>① 발생기실 개구부는 1 [m]가 아니라 1.5 [m] 이상 떨어져야 한다.&lt;br&gt;② 가스집합장치로부터는 3 [m]가 아니라 5 [m] 이내에서 화기 사용을 금한다.&lt;br&gt;③ 흡연 금지 거리는 발생기에서 5 [m], 발생기실에서 3 [m] 이내다.</t>
         </is>
       </c>
       <c r="AI46" s="32" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="AG49" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감지형 방호장치&lt;/strong&gt;다. &lt;strong&gt;이상을 알아채고 스스로 멈추거나 조정&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방호장치의 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;격리형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람과 위험점을 벽으로 나눈다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;완전차단형·덮개형 방호장치&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위치제한형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손이 닿지 않는 거리에 조작부를 둔다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접근거부형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;들어온 손을 밀어낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접근반응형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;들어오면 기계를 멈춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;광전자식&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감지형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이상을 감지해 멈추거나 조정한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과부하방지장치 · 압력제한스위치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포집형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;날아오는 것을 받아 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연삭기 덮개&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;감지형 방호장치&lt;/strong&gt;다. &lt;strong&gt;이상을 알아채고 스스로 멈추거나 조정&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방호장치의 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;격리형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람과 위험점을 벽으로 나눈다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;완전차단형·덮개형 방호장치&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위치제한형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손이 닿지 않는 거리에 조작부를 둔다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접근거부형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;들어온 손을 밀어낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접근반응형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;들어오면 기계를 멈춘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;광전자식&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감지형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이상을 감지해 멈추거나 조정한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;과부하방지장치 · 압력제한스위치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;포집형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;날아오는 것을 받아 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연삭기 덮개&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH49" s="32" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="AH50" s="32" t="inlineStr">
         <is>
-          <t>① 200 [mm] 는 한 손으로도 누를 수 있어 위험하다.&lt;br&gt;② 250 [mm] 도 기준에 못 미친다.&lt;br&gt;④ 400 [mm] 는 기준보다 넓다.</t>
+          <t>① 200 [mm]는 한 손으로도 누를 수 있어 위험하다.&lt;br&gt;② 250 [mm] 도 기준에 못 미친다.&lt;br&gt;④ 400 [mm]는 기준보다 넓다.</t>
         </is>
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치 안전인증 고시 — 양수조작식&lt;/strong&gt;&lt;br&gt;양수조작식은 &lt;strong&gt;두 손을 다 써야 기계가 돈다&lt;/strong&gt;는 원리다. &lt;strong&gt;버튼이 가까우면 팔꿈치나 한 손으로 눌러 무력화&lt;/strong&gt; 되므로 300 [mm] 이상 벌린다. &lt;strong&gt;안전거리 &lt;/strong&gt;$D = 1.6 ( T_{l} + T_{s} )$도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누름버튼 간격 300 [mm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방호장치 안전인증 고시 — 양수조작식&lt;/strong&gt;&lt;br&gt;양수조작식은 &lt;strong&gt;두 손을 다 써야 기계가 돈다&lt;/strong&gt;는 원리다. &lt;strong&gt;버튼이 가까우면 팔꿈치나 한 손으로 눌러 무력화&lt;/strong&gt;되므로 300 [mm] 이상 벌린다. &lt;strong&gt;안전거리 &lt;/strong&gt;$D = 1.6 ( T_{l} + T_{s} )$도 함께 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누름버튼 간격 300 [mm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7631,17 +7631,17 @@
       </c>
       <c r="AG51" s="32" t="inlineStr">
         <is>
-          <t>$\text{극한강도} = \text{안전계수} \times \text{정격하중} = 6 \times 100 = 600$ [kg] 이다.</t>
+          <t>$\text{극한강도} = \text{안전계수} \times \text{정격하중} = 6 \times 100 = 600$ [kg]이다.</t>
         </is>
       </c>
       <c r="AH51" s="32" t="inlineStr">
         <is>
-          <t>① 0.06 은 자릿수가 크게 어긋난다.&lt;br&gt;② 16.67 은 100 을 6 으로 나눈 값이다.&lt;br&gt;③ 26.67 도 계산과 맞지 않는다.</t>
+          <t>① 0.06은 자릿수가 크게 어긋난다.&lt;br&gt;② 16.67은 100을 6으로 나눈 값이다.&lt;br&gt;③ 26.67 도 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI51" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전계수와 극한강도&lt;/strong&gt;&lt;br&gt;$\text{안전계수} = \dfrac{\text{극한강도}}{\text{정격하중}}$ 이므로 &lt;strong&gt;극한강도는 곱셈&lt;/strong&gt;이다. &lt;strong&gt;안전계수가 1보다 크므로 극한강도가 정격하중보다 커야&lt;/strong&gt; 한다는 것으로도 나눗셈 보기가 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;극한강도 = 안전계수 × 정격하중&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전계수와 극한강도&lt;/strong&gt;&lt;br&gt;$\text{안전계수} = \dfrac{\text{극한강도}}{\text{정격하중}}$이므로 &lt;strong&gt;극한강도는 곱셈&lt;/strong&gt;이다. &lt;strong&gt;안전계수가 1보다 크므로 극한강도가 정격하중보다 커야&lt;/strong&gt; 한다는 것으로도 나눗셈 보기가 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;극한강도 = 안전계수 × 정격하중&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="AG52" s="32" t="inlineStr">
         <is>
-          <t>상부틀 개구의 폭이나 길이는 &lt;strong&gt;16 [cm] 미만&lt;/strong&gt; 이라야 한다. 25 [cm] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차 헤드가드의 기준 (규칙 제180조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대하중의 2배(4 [t] 을 넘는 값은 4 [t])의 등분포정하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부틀 개구의 폭·길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;16 [cm] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 [cm] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앉아서 조작 — 좌석 윗면에서 상부틀 아랫면까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;서서 조작 — 운전석 바닥면에서 상부틀 아랫면까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>상부틀 개구의 폭이나 길이는 &lt;strong&gt;16 [cm] 미만&lt;/strong&gt;이라야 한다. 25 [cm]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차 헤드가드의 기준 (규칙 제180조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대하중의 2배(4 [t]을 넘는 값은 4 [t])의 등분포정하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부틀 개구의 폭·길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;16 [cm] 미만&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;25 [cm]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앉아서 조작 — 좌석 윗면에서 상부틀 아랫면까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;서서 조작 — 운전석 바닥면에서 상부틀 아랫면까지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH52" s="32" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="AI52" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제180조 — 헤드가드&lt;/strong&gt;&lt;br&gt;네 숫자를 묶어 둔다 — &lt;strong&gt;2배 · 16 [cm] · 1 [m] · 2 [m]&lt;/strong&gt;. &lt;strong&gt;16 [cm] 는 머리가 빠져나가지 못하는 크기&lt;/strong&gt; 라서 정한 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;개구는 16 [cm] 미만&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C180%EC%A1%B0" target="_blank"&gt;제180조(헤드가드)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 다음 각 호에 따른 적합한 헤드가드(head guard)를 갖추지 아니한 지게차를 사용해서는 안 된다. 다만, 화물의 낙하에 의하여 지게차의 운전자에게 위험을 미칠 우려가 없는 경우에는 그렇지 않다. &amp;lt;개정 2019.1.31, 2022.10.18&amp;gt;&lt;br&gt; 1. 강도는 지게차의 최대하중의 2배 값(4톤을 넘는 값에 대해서는 4톤으로 한다)의 등분포정하중(等分布靜荷重)에 견딜 수 있을 것&lt;br&gt;▶  2. &lt;strong&gt;상부틀의 각 개구의 폭 또는 길이가&lt;/strong&gt; 16센티미터 미만일 것&lt;br&gt; 3. 운전자가 앉아서 조작하거나 서서 조작하는 지게차의 헤드가드는 한국산업표준에서 정하는 높이 기준 이상일 것&lt;br&gt; 4. 삭제&amp;lt;2019.1.31&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제180조 — 헤드가드&lt;/strong&gt;&lt;br&gt;네 숫자를 묶어 둔다 — &lt;strong&gt;2배 · 16 [cm] · 1 [m] · 2 [m]&lt;/strong&gt;. &lt;strong&gt;16 [cm]는 머리가 빠져나가지 못하는 크기&lt;/strong&gt; 라서 정한 값이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;개구는 16 [cm] 미만&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C180%EC%A1%B0" target="_blank"&gt;제180조(헤드가드)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;사업주는 다음 각 호에 따른 적합한 헤드가드(head guard)를 갖추지 아니한 지게차를 사용해서는 안 된다. 다만, 화물의 낙하에 의하여 지게차의 운전자에게 위험을 미칠 우려가 없는 경우에는 그렇지 않다. &amp;lt;개정 2019.1.31, 2022.10.18&amp;gt;&lt;br&gt; 1. 강도는 지게차의 최대하중의 2배 값(4톤을 넘는 값에 대해서는 4톤으로 한다)의 등분포정하중(等分布靜荷重)에 견딜 수 있을 것&lt;br&gt;▶  2. &lt;strong&gt;상부틀의 각 개구의 폭 또는 길이가&lt;/strong&gt; 16센티미터 미만일 것&lt;br&gt; 3. 운전자가 앉아서 조작하거나 서서 조작하는 지게차의 헤드가드는 한국산업표준에서 정하는 높이 기준 이상일 것&lt;br&gt; 4. 삭제&amp;lt;2019.1.31&amp;gt;&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -8023,12 +8023,12 @@
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
-          <t>② 손쳐내기식은 B 가 아니라 D 다.&lt;br&gt;③ 광전자식은 D-1 이 아니라 A-1 이다.&lt;br&gt;④ 양수조작식은 A-1 이 아니라 B-1 이다.</t>
+          <t>② 손쳐내기식은 B가 아니라 D다.&lt;br&gt;③ 광전자식은 D-1이 아니라 A-1이다.&lt;br&gt;④ 양수조작식은 A-1이 아니라 B-1이다.</t>
         </is>
       </c>
       <c r="AI54" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치 안전인증 고시 — 프레스 방호장치의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;A · B · C · D · E 를 광 · 양 · 가 · 손 · 수&lt;/strong&gt; 순으로 잡는다. &lt;strong&gt;A 와 B 만 하위 번호(-1, -2)가 붙는다&lt;/strong&gt;는 것도 함께 기억한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;광 A · 양 B · 가 C · 손 D · 수 E&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방호장치 안전인증 고시 — 프레스 방호장치의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;A · B · C · D · E를 광 · 양 · 가 · 손 · 수&lt;/strong&gt; 순으로 잡는다. &lt;strong&gt;A와 B 만 하위 번호(-1, -2)가 붙는다&lt;/strong&gt;는 것도 함께 기억한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;광 A · 양 B · 가 C · 손 D · 수 E&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="AH55" s="32" t="inlineStr">
         <is>
-          <t>① 15 [mm] 는 기준에 못 미친다.&lt;br&gt;② 20 [mm] 도 그렇다.&lt;br&gt;④ 30 [mm] 는 저압용 기준보다 크지만 규정값이 아니다.</t>
+          <t>① 15 [mm]는 기준에 못 미친다.&lt;br&gt;② 20 [mm] 도 그렇다.&lt;br&gt;④ 30 [mm]는 저압용 기준보다 크지만 규정값이 아니다.</t>
         </is>
       </c>
       <c r="AI55" s="32" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="AI58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;와류탐상검사(ET)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「코일 · 교류 · 유기전압」&lt;/strong&gt;이라는 낱말이 와류탐상을 가리킨다. &lt;strong&gt;전기가 통하는 재료(도전성)&lt;/strong&gt; 라야 쓸 수 있고, &lt;strong&gt;표면과 표면 가까이의 결함&lt;/strong&gt;을 찾는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;코일과 와전류면 ET&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;와류탐상검사(ET)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「코일 · 교류 · 유기전압」&lt;/strong&gt;이라는 낱말이 와류탐상을 가리킨다. &lt;strong&gt;전기가 통하는 재료(도전성)&lt;/strong&gt;라야 쓸 수 있고, &lt;strong&gt;표면과 표면 가까이의 결함&lt;/strong&gt;을 찾는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;코일과 와전류면 ET&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="AI61" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 제104조 — 금형조정작업의 위험 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정비할 때는 「전원을 끊는 것」만으로 부족&lt;/strong&gt; 하다. 유압이 빠지거나 자중으로 내려올 수 있으므로 &lt;strong&gt;물리적으로 괴어 두는 안전블록&lt;/strong&gt;이 필요하다. &lt;strong&gt;프레스 · 리프트 · 곤돌라&lt;/strong&gt;에 공통되는 원리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;금형 조정에는 안전블록&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C104%EC%A1%B0" target="_blank"&gt;제104조(금형조정작업의 위험 방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ 제104조(금형조정작업의 위험 방지) 사업주는 프레스등의 금형을 부착ㆍ해체 또는 조정하는 작업을 할 때에 해당 작업에 종사하는 근로자의 신체가 위험한계 내에 있는 경우 슬라이드가 갑자기 작동함으로써 근로자에게 발생할 우려가 있는 위험을 방지하기 위하여 &lt;strong&gt;안전블록&lt;/strong&gt;을 사용하는 등 필요한 조치를 하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 제104조 — 금형조정작업의 위험 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;정비할 때는 「전원을 끊는 것」만으로 부족&lt;/strong&gt;하다. 유압이 빠지거나 자중으로 내려올 수 있으므로 &lt;strong&gt;물리적으로 괴어 두는 안전블록&lt;/strong&gt;이 필요하다. &lt;strong&gt;프레스 · 리프트 · 곤돌라&lt;/strong&gt;에 공통되는 원리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;금형 조정에는 안전블록&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawart&gt;&lt;div class=h&gt;&lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99/%EC%A0%9C104%EC%A1%B0" target="_blank"&gt;제104조(금형조정작업의 위험 방지)&lt;/a&gt;&lt;span class=eff&gt;산업안전보건기준에 관한 규칙 · 시행 2026. 3. 2.&lt;/span&gt;&lt;/div&gt;&lt;div class=t&gt;▶ 제104조(금형조정작업의 위험 방지) 사업주는 프레스등의 금형을 부착ㆍ해체 또는 조정하는 작업을 할 때에 해당 작업에 종사하는 근로자의 신체가 위험한계 내에 있는 경우 슬라이드가 갑자기 작동함으로써 근로자에게 발생할 우려가 있는 위험을 방지하기 위하여 &lt;strong&gt;안전블록&lt;/strong&gt;을 사용하는 등 필요한 조치를 하여야 한다.&lt;/div&gt;&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -9184,12 +9184,12 @@
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>① 고통을 느끼는 전류는 고통한계전류(7 ~ 8 [mA])다.&lt;br&gt;③ 직류가 아니라 교류가 기준이다.&lt;br&gt;④ 직류 기준이라는 점과 0.7 [mA] 라는 값이 모두 어긋난다.</t>
+          <t>① 고통을 느끼는 전류는 고통한계전류(7 ~ 8 [mA])다.&lt;br&gt;③ 직류가 아니라 교류가 기준이다.&lt;br&gt;④ 직류 기준이라는 점과 0.7 [mA]라는 값이 모두 어긋난다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소감지전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;감전의 기준값은 모두 상용주파수 교류(60 [Hz])&lt;/strong&gt;를 전제한다. &lt;strong&gt;직류는 같은 크기라도 덜 위험&lt;/strong&gt; 해 값이 다르다. 여자는 남자의 약 2/3 로 본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;최소감지전류는 교류 1 [mA]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소감지전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;감전의 기준값은 모두 상용주파수 교류(60 [Hz])&lt;/strong&gt;를 전제한다. &lt;strong&gt;직류는 같은 크기라도 덜 위험&lt;/strong&gt;해 값이 다르다. 여자는 남자의 약 2/3로 본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;최소감지전류는 교류 1 [mA]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9695,17 +9695,17 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>$I = \dfrac{V}{R} = \dfrac{220}{1 {,} 000} = 0.22 \, A = 220 \, \mathrm{mA}$&lt;strong&gt;220mA 는 심실세동을 일으키는 수준&lt;/strong&gt;이라 위험하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;통전전류와 인체의 반응&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;반응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소감지전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;찌릿한 느낌&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고통한계전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;견딜 수 있는 한계&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 ~ 15 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가수전류(이탈전류)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스스로 손을 뗄 수 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;20 ~ 50 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불수전류(교착전류)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육이 굳어 손을 못 뗀다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 ~ 100 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생명이 위험하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;220 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그 한참 위 — 위험&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$I = \dfrac{V}{R} = \dfrac{220}{1 {,} 000} = 0.22 \, A = 220 \, \mathrm{mA}$&lt;strong&gt;220mA는 심실세동을 일으키는 수준&lt;/strong&gt;이라 위험하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;통전전류와 인체의 반응&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;전류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;반응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최소감지전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;찌릿한 느낌&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고통한계전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;견딜 수 있는 한계&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10 ~ 15 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;가수전류(이탈전류)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;스스로 손을 뗄 수 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;20 ~ 50 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;불수전류(교착전류)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근육이 굳어 손을 못 뗀다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 ~ 100 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생명이 위험하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;220 mA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그 한참 위 — 위험&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>① 10mA 는 계산과 맞지 않는다.&lt;br&gt;② 45mA 도 그렇다.&lt;br&gt;③ 50mA 도 그렇고, 50mA 는 이미 안전하지도 않다.</t>
+          <t>① 10mA는 계산과 맞지 않는다.&lt;br&gt;② 45mA 도 그렇다.&lt;br&gt;③ 50mA 도 그렇고, 50mA는 이미 안전하지도 않다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감전전류의 계산과 위험성&lt;/strong&gt;&lt;br&gt;$I = \dfrac{V}{R}$로 먼저 셈한다 — &lt;strong&gt;220 ÷ 1,000 = 0.22A = 220mA&lt;/strong&gt;다. &lt;strong&gt;50mA 만 넘어도 심실세동&lt;/strong&gt; 이니 220mA 는 두말할 것 없이 위험하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;220V·1,000Ω → 220mA, 위험&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;감전전류의 계산과 위험성&lt;/strong&gt;&lt;br&gt;$I = \dfrac{V}{R}$로 먼저 셈한다 — &lt;strong&gt;220 ÷ 1,000 = 0.22A = 220mA&lt;/strong&gt;다. &lt;strong&gt;50mA 만 넘어도 심실세동&lt;/strong&gt; 이니 220mA는 두말할 것 없이 위험하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;220V·1,000Ω → 220mA, 위험&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9824,17 +9824,17 @@
       </c>
       <c r="AG68" s="32" t="inlineStr">
         <is>
-          <t>$I = V / R = 220 / 1 {,} 000 = 0.22$ [A] = &lt;strong&gt;220 [mA]&lt;/strong&gt;다. &lt;strong&gt;심실세동전류(50 [mA])를 훨씬 넘어 위험&lt;/strong&gt; 하다.</t>
+          <t>$I = V / R = 220 / 1 {,} 000 = 0.22$ [A] = &lt;strong&gt;220 [mA]&lt;/strong&gt;다. &lt;strong&gt;심실세동전류(50 [mA])를 훨씬 넘어 위험&lt;/strong&gt;하다.</t>
         </is>
       </c>
       <c r="AH68" s="32" t="inlineStr">
         <is>
-          <t>① 22 [mA] 는 계산이 열 배 어긋난 값이다.&lt;br&gt;② 220 [mA] 는 맞지만 안전하지 않다.&lt;br&gt;③ 22 [mA] 라는 값 자체가 어긋난다.</t>
+          <t>① 22 [mA]는 계산이 열 배 어긋난 값이다.&lt;br&gt;② 220 [mA]는 맞지만 안전하지 않다.&lt;br&gt;③ 22 [mA]라는 값 자체가 어긋난다.</t>
         </is>
       </c>
       <c r="AI68" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;옴의 법칙과 감전 위험&lt;/strong&gt;&lt;br&gt;$I = V / R$ 로 곧바로 나온다. &lt;strong&gt;220 [mA] 는 심실세동전류의 네 배가 넘어&lt;/strong&gt; 목숨이 위태롭다. &lt;strong&gt;우리가 늘 쓰는 220 [V] 가 얼마나 위험한지&lt;/strong&gt;를 보여 주는 계산이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;220 [V] ÷ 1,000 [Ω] = 220 [mA]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;옴의 법칙과 감전 위험&lt;/strong&gt;&lt;br&gt;$I = V / R$로 곧바로 나온다. &lt;strong&gt;220 [mA]는 심실세동전류의 네 배가 넘어&lt;/strong&gt; 목숨이 위태롭다. &lt;strong&gt;우리가 늘 쓰는 220 [V]가 얼마나 위험한지&lt;/strong&gt;를 보여 주는 계산이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;220 [V] ÷ 1,000 [Ω] = 220 [mA]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9945,17 +9945,17 @@
       </c>
       <c r="AG69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;90 [cm]&lt;/strong&gt;다. 22.9 [kV] 는 &lt;strong&gt;15 [kV] 초과 37 [kV] 이하&lt;/strong&gt; 구간에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;충전전로에 대한 접근한계거리 (규칙 별표5)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;충전전로의 선간전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접근한계거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.3 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;접촉금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.3 초과 0.75 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.75 초과 2 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;45 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2 초과 15 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;15 초과 37 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;22.9 [kV] 가 여기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;37 초과 88 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;110 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;90 [cm]&lt;/strong&gt;다. 22.9 [kV]는 &lt;strong&gt;15 [kV] 초과 37 [kV] 이하&lt;/strong&gt; 구간에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;충전전로에 대한 접근한계거리 (규칙 별표5)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;충전전로의 선간전압&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;접근한계거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.3 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;접촉금지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.3 초과 0.75 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.75 초과 2 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;45 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2 초과 15 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;15 초과 37 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;22.9 [kV]가 여기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;37 초과 88 [kV] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;110 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 45 [cm] 는 0.75 ~ 2 [kV] 구간이다.&lt;br&gt;② 60 [cm] 는 2 ~ 15 [kV] 구간이다.&lt;br&gt;④ 110 [cm] 는 37 ~ 88 [kV] 구간이다.</t>
+          <t>① 45 [cm]는 0.75 ~ 2 [kV] 구간이다.&lt;br&gt;② 60 [cm]는 2 ~ 15 [kV] 구간이다.&lt;br&gt;④ 110 [cm]는 37 ~ 88 [kV] 구간이다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 별표5 — 충전전로에 대한 접근한계거리&lt;/strong&gt;&lt;br&gt;앞부분을 &lt;strong&gt;30 · 45 · 60 · 90 · 110&lt;/strong&gt;으로 잡고, 구간 경계를 &lt;strong&gt;0.75 · 2 · 15 · 37 · 88 [kV]&lt;/strong&gt;로 짝지어 둔다. &lt;strong&gt;22.9 [kV] 는 우리나라 배전선로의 표준전압&lt;/strong&gt;이라 자주 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;22.9 [kV] 는 90 [cm]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 5&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 별표5 — 충전전로에 대한 접근한계거리&lt;/strong&gt;&lt;br&gt;앞부분을 &lt;strong&gt;30 · 45 · 60 · 90 · 110&lt;/strong&gt;으로 잡고, 구간 경계를 &lt;strong&gt;0.75 · 2 · 15 · 37 · 88 [kV]&lt;/strong&gt;로 짝지어 둔다. &lt;strong&gt;22.9 [kV]는 우리나라 배전선로의 표준전압&lt;/strong&gt;이라 자주 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;22.9 [kV]는 90 [cm]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 5&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -10071,12 +10071,12 @@
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 직류 저압은 교류의 √2배가 아니라 따로 정해진 값(옛 750 [V], 현행 1,500 [V])이다.&lt;br&gt;② 고압의 상한은 교류·직류 모두 7,000 [V] 로 같다.&lt;br&gt;④ 7,500 [V] 라는 경계는 어느 기준에도 없다.</t>
+          <t>① 직류 저압은 교류의 √2배가 아니라 따로 정해진 값(옛 750 [V], 현행 1,500 [V])이다.&lt;br&gt;② 고압의 상한은 교류·직류 모두 7,000 [V]로 같다.&lt;br&gt;④ 7,500 [V]라는 경계는 어느 기준에도 없다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전압의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;특고압의 경계 7,000 [V] 는 교직 공통이며 개정에도 그대로&lt;/strong&gt;다. 그래서 &lt;strong&gt;개정 전 문항이라도 보기 ③은 지금도 맞는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;특고압은 교직 모두 7,000 [V] 초과&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 &lt;u&gt;저압의 범위가 교류 1,000 [V] 이하 · 직류 1,500 [V] 이하&lt;/u&gt;로 넓어졌다. 이 문항은 &lt;u&gt;개정 전 기준(교류 600 [V] · 직류 750 [V])&lt;/u&gt;을 전제로 출제되었으나, &lt;u&gt;정답인 보기 ③(특고압 7,000 [V] 초과)은 현행 기준으로도 옳다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전압의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;특고압의 경계 7,000 [V]는 교직 공통이며 개정에도 그대로&lt;/strong&gt;다. 그래서 &lt;strong&gt;개정 전 문항이라도 보기 ③은 지금도 맞는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;특고압은 교직 모두 7,000 [V] 초과&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;2021. 1. 1. KEC 시행&lt;/u&gt;으로 &lt;u&gt;저압의 범위가 교류 1,000 [V] 이하 · 직류 1,500 [V] 이하&lt;/u&gt;로 넓어졌다. 이 문항은 &lt;u&gt;개정 전 기준(교류 600 [V] · 직류 750 [V])&lt;/u&gt;을 전제로 출제되었으나, &lt;u&gt;정답인 보기 ③(특고압 7,000 [V] 초과)은 현행 기준으로도 옳다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10324,12 +10324,12 @@
       </c>
       <c r="AG72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;T1 은 450 [℃] 이하&lt;/strong&gt;가 맞다. 나머지 셋은 값이 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭기기의 온도등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;450 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①이 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②는 350 이라 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③은 125 라 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④는 100 이라 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;T1은 450 [℃] 이하&lt;/strong&gt;가 맞다. 나머지 셋은 값이 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭기기의 온도등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최고표면온도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기와의 대응&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;450 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①이 맞다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②는 350이라 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;200 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;135 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③은 125 라 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;85 [℃] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④는 100이라 어긋난다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH72" s="32" t="inlineStr">
         <is>
-          <t>② T2 는 350 이 아니라 300 [℃] 이하다.&lt;br&gt;③ T4 는 125 가 아니라 135 [℃] 이하다.&lt;br&gt;④ T6 는 100 이 아니라 85 [℃] 이하다.</t>
+          <t>② T2는 350이 아니라 300 [℃] 이하다.&lt;br&gt;③ T4는 125가 아니라 135 [℃] 이하다.&lt;br&gt;④ T6는 100이 아니라 85 [℃] 이하다.</t>
         </is>
       </c>
       <c r="AI72" s="32" t="inlineStr">
@@ -10969,17 +10969,17 @@
       </c>
       <c r="AG77" s="32" t="inlineStr">
         <is>
-          <t>최대공급전류는 $I = \dfrac{50 {,} 000}{\sqrt{3} \times 380} \fallingdotseq 76$ [A] 다. 누설전류 허용값은 &lt;strong&gt;최대공급전류의 1/2,000&lt;/strong&gt;이므로 $76 / 2 {,} 000 = 0.038$ [A] = &lt;strong&gt;38 [mA]&lt;/strong&gt;다.</t>
+          <t>최대공급전류는 $I = \dfrac{50 {,} 000}{\sqrt{3} \times 380} \fallingdotseq 76$ [A]다. 누설전류 허용값은 &lt;strong&gt;최대공급전류의 1/2,000&lt;/strong&gt;이므로 $76 / 2 {,} 000 = 0.038$ [A] = &lt;strong&gt;38 [mA]&lt;/strong&gt;다.</t>
         </is>
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>① 10 [mA] 는 계산과 맞지 않는다.&lt;br&gt;③ 54 [mA] 도 맞지 않는다.&lt;br&gt;④ 76 [mA] 는 최대공급전류 [A] 값을 그대로 옮긴 것이다.</t>
+          <t>① 10 [mA]는 계산과 맞지 않는다.&lt;br&gt;③ 54 [mA] 도 맞지 않는다.&lt;br&gt;④ 76 [mA]는 최대공급전류 [A] 값을 그대로 옮긴 것이다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누설전류의 허용값&lt;/strong&gt;&lt;br&gt;두 단계다 — &lt;strong&gt;3상 전류 &lt;/strong&gt;$I = P / ( \sqrt{3} V )$&lt;strong&gt; 로 76 [A] 를 구하고, 1/2,000 을 곱한다&lt;/strong&gt;. &lt;strong&gt;「1/2,000」&lt;/strong&gt;이라는 값을 기억하는 것이 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누설전류의 허용값&lt;/strong&gt;&lt;br&gt;두 단계다 — &lt;strong&gt;3상 전류 &lt;/strong&gt;$I = P / ( \sqrt{3} V )$&lt;strong&gt;로 76 [A]를 구하고, 1/2,000을 곱한다&lt;/strong&gt;. &lt;strong&gt;「1/2,000」&lt;/strong&gt;이라는 값을 기억하는 것이 갈림길이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;누설전류는 최대공급전류의 1/2,000&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11361,7 +11361,7 @@
       </c>
       <c r="AH80" s="32" t="inlineStr">
         <is>
-          <t>② 100 [Ω] 이하는 제3종 접지공사의 값이다.&lt;br&gt;③ 106 [Ω] 이라는 기준은 없다.&lt;br&gt;④ 1 [kΩ] 은 지나치게 높다.</t>
+          <t>② 100 [Ω] 이하는 제3종 접지공사의 값이다.&lt;br&gt;③ 106 [Ω]이라는 기준은 없다.&lt;br&gt;④ 1 [kΩ]은 지나치게 높다.</t>
         </is>
       </c>
       <c r="AI80" s="32" t="inlineStr">
@@ -11490,12 +11490,12 @@
       </c>
       <c r="AH81" s="32" t="inlineStr">
         <is>
-          <t>② 12.5 [kV] 는 계산과 맞지 않는다.&lt;br&gt;③ 14.4 [kV] 는 반지름을 0.125 [m] 로 잘못 놓았을 때 나온다.&lt;br&gt;④ 25 [kV] 도 맞지 않는다.</t>
+          <t>② 12.5 [kV]는 계산과 맞지 않는다.&lt;br&gt;③ 14.4 [kV]는 반지름을 0.125 [m]로 잘못 놓았을 때 나온다.&lt;br&gt;④ 25 [kV] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI81" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;도체구의 전위&lt;/strong&gt;&lt;br&gt;$V = 9 \times 10^{9} \times Q / r$ 다. &lt;strong&gt;반지름을 [cm] 그대로 넣지 않고 [m] 로 바꾸는 것&lt;/strong&gt;이 갈림길이다. &lt;strong&gt;2 × 10⁻⁷ [C] 이라는 작은 전하로도 7.2 [kV] 가 걸린다&lt;/strong&gt;는 점이 정전기의 위험을 말해 준다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = 9 \times 10^{9} Q / r$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;도체구의 전위&lt;/strong&gt;&lt;br&gt;$V = 9 \times 10^{9} \times Q / r$다. &lt;strong&gt;반지름을 [cm] 그대로 넣지 않고 [m]로 바꾸는 것&lt;/strong&gt;이 갈림길이다. &lt;strong&gt;2 × 10⁻⁷ [C]이라는 작은 전하로도 7.2 [kV]가 걸린다&lt;/strong&gt;는 점이 정전기의 위험을 말해 준다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $V = 9 \times 10^{9} Q / r$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="AG83" s="32" t="inlineStr">
         <is>
-          <t>인산은 &lt;strong&gt;농도 60 [%] 이상&lt;/strong&gt; 이라야 부식성 산류다. 40 [%] 는 들지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;부식성 물질의 농도 기준 (규칙 별표1)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질과 농도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 산류 — 강한 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;농도 20 [%] 이상인 염산 · 황산 · 질산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 산류 — 그 밖의 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;농도 60 [%] 이상인 인산 · 아세트산 · 불산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 염기류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;농도 40 [%] 이상인 수산화나트륨 · 수산화칼륨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>인산은 &lt;strong&gt;농도 60 [%] 이상&lt;/strong&gt;이라야 부식성 산류다. 40 [%]는 들지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;부식성 물질의 농도 기준 (규칙 별표1)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;물질과 농도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 산류 — 강한 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;농도 20 [%] 이상인 염산 · 황산 · 질산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 산류 — 그 밖의 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;농도 60 [%] 이상인 인산 · 아세트산 · 불산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;60 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;부식성 염기류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;농도 40 [%] 이상인 수산화나트륨 · 수산화칼륨&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [%]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH83" s="32" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="AI83" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전보건규칙 별표1 — 부식성 물질&lt;/strong&gt;&lt;br&gt;세 숫자를 잡는다 — &lt;strong&gt;강산 20 · 그 밖의 산 60 · 염기 40&lt;/strong&gt;. &lt;strong&gt;염산·황산·질산은 강해서 20 [%] 부터, 인산·아세트산·불산은 약해서 60 [%] 부터&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;강산 20, 그 밖의 산 60, 염기 40&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 1&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전보건규칙 별표1 — 부식성 물질&lt;/strong&gt;&lt;br&gt;세 숫자를 잡는다 — &lt;strong&gt;강산 20 · 그 밖의 산 60 · 염기 40&lt;/strong&gt;. &lt;strong&gt;염산·황산·질산은 강해서 20 [%]부터, 인산·아세트산·불산은 약해서 60 [%]부터&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;강산 20, 그 밖의 산 60, 염기 40&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚖ 근거 법령&lt;/strong&gt; &lt;span class="eff"&gt;산업안전보건기준에 관한 규칙 시행 2026. 3. 2.&lt;/span&gt;&lt;/p&gt;&lt;div class=lawmiss&gt;· &lt;a href="https://www.law.go.kr/법령/%EC%82%B0%EC%97%85%EC%95%88%EC%A0%84%EB%B3%B4%EA%B1%B4%EA%B8%B0%EC%A4%80%EC%97%90%EA%B4%80%ED%95%9C%EA%B7%9C%EC%B9%99" target="_blank"&gt;산업안전보건기준에 관한 규칙 별표 1&lt;/a&gt; — 별표는 법제처 원문에서 봅니다&lt;/div&gt;</t>
         </is>
       </c>
     </row>
@@ -11872,17 +11872,17 @@
       </c>
       <c r="AG84" s="32" t="inlineStr">
         <is>
-          <t>$T_{2} = T_{1} ( \dfrac{P_{2}}{P_{1}} )^{( k - 1 ) / k} = 293 \times 5^{0.4 / 1.4} \fallingdotseq 293 \times 1.584 = 464$ [K] 다. 섭씨로 바꾸면 $464 - 273 = 191$ [℃] 다.</t>
+          <t>$T_{2} = T_{1} ( \dfrac{P_{2}}{P_{1}} )^{( k - 1 ) / k} = 293 \times 5^{0.4 / 1.4} \fallingdotseq 293 \times 1.584 = 464$ [K]다. 섭씨로 바꾸면 $464 - 273 = 191$ [℃]다.</t>
         </is>
       </c>
       <c r="AH84" s="32" t="inlineStr">
         <is>
-          <t>① 32 [℃] 는 계산과 맞지 않는다.&lt;br&gt;③ 305 [℃] 도 맞지 않는다.&lt;br&gt;④ 464 는 켈빈 값을 그대로 옮긴 것이다.</t>
+          <t>① 32 [℃]는 계산과 맞지 않는다.&lt;br&gt;③ 305 [℃] 도 맞지 않는다.&lt;br&gt;④ 464는 켈빈 값을 그대로 옮긴 것이다.</t>
         </is>
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;단열압축과 온도 상승&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;켈빈으로 바꿔 계산하고 다시 섭씨로 돌려놓는&lt;/strong&gt; 두 단계를 놓치면 464 를 골라 틀린다. &lt;strong&gt;압축하면 온도가 오른다&lt;/strong&gt;는 것이 &lt;strong&gt;디젤 엔진의 자기착화와 압축기 화재&lt;/strong&gt;의 원리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T_{2} = T_{1} ( P_{2} / P_{1} )^{( k - 1 ) / k}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;단열압축과 온도 상승&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;켈빈으로 바꿔 계산하고 다시 섭씨로 돌려놓는&lt;/strong&gt; 두 단계를 놓치면 464를 골라 틀린다. &lt;strong&gt;압축하면 온도가 오른다&lt;/strong&gt;는 것이 &lt;strong&gt;디젤 엔진의 자기착화와 압축기 화재&lt;/strong&gt;의 원리다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T_{2} = T_{1} ( P_{2} / P_{1} )^{( k - 1 ) / k}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12135,7 +12135,7 @@
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>① 액과 액이 닿아야 폭발이 일어나는 것은 맞다.&lt;br&gt;③ 증기폭발에 확률적 요소가 있는 것도 맞다.&lt;br&gt;④ 접촉 후 수~수백 [ms] 의 지연이 있고 폭발 자체는 5 [ms] 이하인 것도 맞다.</t>
+          <t>① 액과 액이 닿아야 폭발이 일어나는 것은 맞다.&lt;br&gt;③ 증기폭발에 확률적 요소가 있는 것도 맞다.&lt;br&gt;④ 접촉 후 수~수백 [ms]의 지연이 있고 폭발 자체는 5 [ms] 이하인 것도 맞다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="AI87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화의 방지&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt; 일 때 일어난다. &lt;strong&gt;방열을 늘리는 것(통풍)이 가장 확실한 대책&lt;/strong&gt; 인데, &lt;strong&gt;밀폐는 그 반대&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;밀폐가 아니라 통풍&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화의 방지&lt;/strong&gt;&lt;br&gt;자연발화는 &lt;strong&gt;발열 &amp;gt; 방열&lt;/strong&gt;일 때 일어난다. &lt;strong&gt;방열을 늘리는 것(통풍)이 가장 확실한 대책&lt;/strong&gt; 인데, &lt;strong&gt;밀폐는 그 반대&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;밀폐가 아니라 통풍&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12388,7 +12388,7 @@
       </c>
       <c r="AG88" s="32" t="inlineStr">
         <is>
-          <t>$C_{2} H_{5} OH + 3 O_{2} \rightarrow 2 CO_{2} + 3 H_{2} O$ 다. &lt;strong&gt;탄소 2개는 CO₂ 2몰, 수소 6개는 H₂O 3몰&lt;/strong&gt;이 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;완전연소 생성물의 몰수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;분자 속 개수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;생성물&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄소 C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;CO₂ 2몰&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 H&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;H₂O 3몰&lt;/u&gt; (H 2개당 물 1몰)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 O&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;반응식의 산소 계수를 줄인다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$C_{2} H_{5} OH + 3 O_{2} \rightarrow 2 CO_{2} + 3 H_{2} O$다. &lt;strong&gt;탄소 2개는 CO₂ 2몰, 수소 6개는 H₂O 3몰&lt;/strong&gt;이 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;완전연소 생성물의 몰수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;분자 속 개수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;생성물&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;탄소 C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;CO₂ 2몰&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 H&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;H₂O 3몰&lt;/u&gt; (H 2개당 물 1몰)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 O&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;반응식의 산소 계수를 줄인다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH88" s="32" t="inlineStr">
@@ -12483,7 +12483,7 @@
       </c>
       <c r="U89" s="32" t="inlineStr">
         <is>
-          <t>6vol% 헥산, 4vol% 메탄, 2vol% 에틸렌으로 구성된 혼합가스의 연소하한값(LFL)은 약 얼마인가? (단, 각 물질의 공기 중 연소하한값은 헥산은 1.1vol%, 메탄은 5.0vol%, 에틸렌은 2.7vol% 이다.)</t>
+          <t>6vol% 헥산, 4vol% 메탄, 2vol% 에틸렌으로 구성된 혼합가스의 연소하한값(LFL)은 약 얼마인가? (단, 각 물질의 공기 중 연소하한값은 헥산은 1.1vol%, 메탄은 5.0vol%, 에틸렌은 2.7vol%이다.)</t>
         </is>
       </c>
       <c r="V89" s="32" t="inlineStr"/>
@@ -12517,17 +12517,17 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>가연성 가스의 합이 12 [vol%] 이므로 헥산 50, 메탄 33.3, 에틸렌 16.7 [%] 로 환산한다. $\dfrac{100}{L} = \dfrac{50}{1.1} + \dfrac{33.3}{5.0} + \dfrac{16.7}{2.7} = 45.45 + 6.67 + 6.19 = 58.31$ 이므로 $L = 100 / 58.31 \fallingdotseq 1.71$ [vol%] 다.</t>
+          <t>가연성 가스의 합이 12 [vol%]이므로 헥산 50, 메탄 33.3, 에틸렌 16.7 [%]로 환산한다. $\dfrac{100}{L} = \dfrac{50}{1.1} + \dfrac{33.3}{5.0} + \dfrac{16.7}{2.7} = 45.45 + 6.67 + 6.19 = 58.31$이므로 $L = 100 / 58.31 \fallingdotseq 1.71$ [vol%]다.</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>① 0.69 [vol%] 는 환산을 잘못했을 때 나온다.&lt;br&gt;② 1.21 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 1.45 [vol%] 는 조성이 다른 경우의 값이다.</t>
+          <t>① 0.69 [vol%]는 환산을 잘못했을 때 나온다.&lt;br&gt;② 1.21 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 1.45 [vol%]는 조성이 다른 경우의 값이다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;르 샤틀리에(Le Chatelier)의 법칙&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$ 다. &lt;strong&gt;공기가 섞여 있으면 반드시 가연성 가스끼리 다시 100 [%] 로 환산&lt;/strong&gt; 한다. &lt;strong&gt;결과는 늘 가장 낮은 하한값(1.1)보다 조금 큰 값&lt;/strong&gt;이 되므로 검산이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기를 빼고 다시 100 [%] 로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;르 샤틀리에(Le Chatelier)의 법칙&lt;/strong&gt;&lt;br&gt;$\dfrac{100}{L} = \sum \dfrac{V_{i}}{L_{i}}$다. &lt;strong&gt;공기가 섞여 있으면 반드시 가연성 가스끼리 다시 100 [%]로 환산&lt;/strong&gt;한다. &lt;strong&gt;결과는 늘 가장 낮은 하한값(1.1)보다 조금 큰 값&lt;/strong&gt;이 되므로 검산이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기를 빼고 다시 100 [%]로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12904,7 +12904,7 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세트산 농도 90 [%] 는 부식성 산류&lt;/strong&gt;다. 60 [%] 이상이면 여기에 든다.</t>
+          <t>&lt;strong&gt;아세트산 농도 90 [%]는 부식성 산류&lt;/strong&gt;다. 60 [%] 이상이면 여기에 든다.</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
@@ -13167,12 +13167,12 @@
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>① 일산화탄소는 30 [ppm] 으로 포스겐보다 훨씬 높다.&lt;br&gt;③ 암모니아는 25 [ppm] 이다.&lt;br&gt;④ 시안화수소는 10 [ppm] 이다.</t>
+          <t>① 일산화탄소는 30 [ppm]으로 포스겐보다 훨씬 높다.&lt;br&gt;③ 암모니아는 25 [ppm]이다.&lt;br&gt;④ 시안화수소는 10 [ppm]이다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;독성가스의 허용농도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;허용농도가 낮을수록 독하다&lt;/strong&gt;. &lt;strong&gt;포스겐 0.1 · 시안화수소 10 · 암모니아 25 · 일산화탄소 30 [ppm]&lt;/strong&gt; 네 값을 잡아 둔다. &lt;strong&gt;일산화탄소는 독성보다는 양이 많아&lt;/strong&gt; 화재 사망의 주범이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;포스겐 0.1 [ppm] 이 가장 독하다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;독성가스의 허용농도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;허용농도가 낮을수록 독하다&lt;/strong&gt;. &lt;strong&gt;포스겐 0.1 · 시안화수소 10 · 암모니아 25 · 일산화탄소 30 [ppm]&lt;/strong&gt; 네 값을 잡아 둔다. &lt;strong&gt;일산화탄소는 독성보다는 양이 많아&lt;/strong&gt; 화재 사망의 주범이 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;포스겐 0.1 [ppm]이 가장 독하다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;금속화재(D급)의 소화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;금속화재에 물 · 이산화탄소 · 할론은 모두 금물&lt;/strong&gt;이다. 물과는 수소를, 이산화탄소와는 탄소를 내며 &lt;strong&gt;오히려 불을 키운다&lt;/strong&gt;. 쓸 수 있는 것은 &lt;strong&gt;건조사 · 팽창질석 · 금속화재용 분말&lt;/strong&gt; 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;금속분말에 물은 금물&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;금속화재(D급)의 소화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;금속화재에 물 · 이산화탄소 · 할론은 모두 금물&lt;/strong&gt;이다. 물과는 수소를, 이산화탄소와는 탄소를 내며 &lt;strong&gt;오히려 불을 키운다&lt;/strong&gt;. 쓸 수 있는 것은 &lt;strong&gt;건조사 · 팽창질석 · 금속화재용 분말&lt;/strong&gt;뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;금속분말에 물은 금물&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13909,7 +13909,7 @@
       <c r="W100" s="32" t="inlineStr"/>
       <c r="X100" s="32" t="inlineStr">
         <is>
-          <t>폭발효율은 BLEVE 보다 크다.</t>
+          <t>폭발효율은 BLEVE보다 크다.</t>
         </is>
       </c>
       <c r="Y100" s="32" t="inlineStr"/>
@@ -13936,12 +13936,12 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;증기운이 커질수록 불씨를 만날 확률이 높아진다&lt;/strong&gt;. 나머지 셋은 모두 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;증기운폭발(UVCE)의 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증기운이 클수록 점화 확률이 높아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발효율은 낮다&lt;/u&gt; (연소에너지의 20 [%] 안팎)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;BLEVE 보다 작다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가장 좋은 대책은 누설 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;점화 방지가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방출점에서 멀리서 점화될수록 충격이 커진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;난류 혼합이 진행되기 때문&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;증기운이 커질수록 불씨를 만날 확률이 높아진다&lt;/strong&gt;. 나머지 셋은 모두 어긋난다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;증기운폭발(UVCE)의 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;증기운이 클수록 점화 확률이 높아진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발효율은 낮다&lt;/u&gt; (연소에너지의 20 [%] 안팎)&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;BLEVE보다 작다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가장 좋은 대책은 누설 방지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;점화 방지가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방출점에서 멀리서 점화될수록 충격이 커진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;난류 혼합이 진행되기 때문&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
         <is>
-          <t>① 폭발효율은 BLEVE 보다 작다.&lt;br&gt;③ 가장 좋은 대책은 점화 방지가 아니라 누설 자체를 막는 것이다.&lt;br&gt;④ 먼 지점에서의 점화는 충격을 오히려 키운다.</t>
+          <t>① 폭발효율은 BLEVE보다 작다.&lt;br&gt;③ 가장 좋은 대책은 점화 방지가 아니라 누설 자체를 막는 것이다.&lt;br&gt;④ 먼 지점에서의 점화는 충격을 오히려 키운다.</t>
         </is>
       </c>
       <c r="AI100" s="32" t="inlineStr">
@@ -14070,12 +14070,12 @@
       </c>
       <c r="AH101" s="32" t="inlineStr">
         <is>
-          <t>① 1.0 [vol%] 는 벤젠의 하한보다 낮다.&lt;br&gt;③ 2.0 [vol%] 는 하한보다 높다.&lt;br&gt;④ 2.5 [vol%] 는 아세톤의 하한값이다.</t>
+          <t>① 1.0 [vol%]는 벤젠의 하한보다 낮다.&lt;br&gt;③ 2.0 [vol%]는 하한보다 높다.&lt;br&gt;④ 2.5 [vol%]는 아세톤의 하한값이다.</t>
         </is>
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;벤젠의 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;벤젠과 가솔린은 하한이 1.4 [vol%] 로 거의 같다&lt;/strong&gt;. 둘 다 &lt;strong&gt;인화점이 영하&lt;/strong&gt;라 상온에서 늘 증기가 나온다. 벤젠은 &lt;strong&gt;발암성 물질&lt;/strong&gt; 이기도 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;벤젠 1.4 ~ 7.1&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;벤젠의 폭발범위&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;벤젠과 가솔린은 하한이 1.4 [vol%]로 거의 같다&lt;/strong&gt;. 둘 다 &lt;strong&gt;인화점이 영하&lt;/strong&gt;라 상온에서 늘 증기가 나온다. 벤젠은 &lt;strong&gt;발암성 물질&lt;/strong&gt; 이기도 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;벤젠 1.4 ~ 7.1&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AH105" s="32" t="inlineStr">
         <is>
-          <t>① 3 [m] 라는 기준은 없다.&lt;br&gt;③ 6 [m] 는 틀비계의 수직방향 값이다.&lt;br&gt;④ 10 [m] 도 기준에 없다.</t>
+          <t>① 3 [m]라는 기준은 없다.&lt;br&gt;③ 6 [m]는 틀비계의 수직방향 값이다.&lt;br&gt;④ 10 [m] 도 기준에 없다.</t>
         </is>
       </c>
       <c r="AI105" s="32" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① 110 [kgf] 는 5 [cm] 매듭 있는 방망의 신품 값이다.&lt;br&gt;③ 360 [kgf] 는 어느 칸에도 없다.&lt;br&gt;④ 400 [kgf] 도 없다.</t>
+          <t>① 110 [kgf]는 5 [cm] 매듭 있는 방망의 신품 값이다.&lt;br&gt;③ 360 [kgf]는 어느 칸에도 없다.&lt;br&gt;④ 400 [kgf] 도 없다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
@@ -15226,17 +15226,17 @@
       </c>
       <c r="AG110" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;50/3 은 50회를 쳤을 때 3 [cm] 만 들어갔다&lt;/strong&gt;는 뜻이다. &lt;strong&gt;앞이 타격횟수, 뒤가 굴진수치&lt;/strong&gt;로 뒤바뀌어 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;표준관입시험(SPT)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;추의 무게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;63.5 [kg]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;낙하 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;76 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관입 깊이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이때의 타격횟수가 N 값&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50/3 의 뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50회 타격에 3 [cm] 관입&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞이 타격횟수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;알맞은 지반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사질토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;점토는 편차가 크다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;50/3은 50회를 쳤을 때 3 [cm] 만 들어갔다&lt;/strong&gt;는 뜻이다. &lt;strong&gt;앞이 타격횟수, 뒤가 굴진수치&lt;/strong&gt;로 뒤바뀌어 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;표준관입시험(SPT)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;추의 무게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;63.5 [kg]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;낙하 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;76 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관입 깊이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [cm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이때의 타격횟수가 N 값&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50/3의 뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50회 타격에 3 [cm] 관입&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞이 타격횟수&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;알맞은 지반&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사질토&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;점토는 편차가 크다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH110" s="32" t="inlineStr">
         <is>
-          <t>① N 값이 30 [cm] 관입에 필요한 타격횟수인 것은 맞다.&lt;br&gt;③ 63.5 [kg] 추를 76 [cm] 에서 자유낙하시키는 것도 맞다.&lt;br&gt;④ 사질지반에 적용하고 점토지반에서 신뢰성이 떨어지는 것도 맞다.</t>
+          <t>① N 값이 30 [cm] 관입에 필요한 타격횟수인 것은 맞다.&lt;br&gt;③ 63.5 [kg] 추를 76 [cm]에서 자유낙하시키는 것도 맞다.&lt;br&gt;④ 사질지반에 적용하고 점토지반에서 신뢰성이 떨어지는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI110" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;표준관입시험(SPT)&lt;/strong&gt;&lt;br&gt;세 숫자를 잡는다 — &lt;strong&gt;63.5 [kg] · 76 [cm] · 30 [cm]&lt;/strong&gt;. &lt;strong&gt;50/3 처럼 분수로 적는 것은 50회를 쳐도 30 [cm] 를 못 들어갈 만큼 단단한 지반&lt;/strong&gt;이라는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;63.5 [kg] · 76 [cm] · 30 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;표준관입시험(SPT)&lt;/strong&gt;&lt;br&gt;세 숫자를 잡는다 — &lt;strong&gt;63.5 [kg] · 76 [cm] · 30 [cm]&lt;/strong&gt;. &lt;strong&gt;50/3 처럼 분수로 적는 것은 50회를 쳐도 30 [cm]를 못 들어갈 만큼 단단한 지반&lt;/strong&gt;이라는 뜻이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;63.5 [kg] · 76 [cm] · 30 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15742,7 +15742,7 @@
       </c>
       <c r="AG114" s="32" t="inlineStr">
         <is>
-          <t>작업발판 위에서 &lt;strong&gt;받침대나 사다리를 쓰면 안 된다&lt;/strong&gt;. 무게중심이 높아져 &lt;strong&gt;비계가 통째로 넘어진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이동식비계의 준수사항 (규칙 제68조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;준수사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바퀴에 브레이크·쐐기 등으로 갑작스러운 이동을 막고, 아웃트리거를 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강용 사다리는 견고하게 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계의 최상부에서 작업할 때는 안전난간을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판 위에서 안전난간을 딛고 작업하거나 받침대·사다리를 사용하지 말 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「사용할 것」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판의 최대적재하중은 250 [kg] 을 초과하지 말 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>작업발판 위에서 &lt;strong&gt;받침대나 사다리를 쓰면 안 된다&lt;/strong&gt;. 무게중심이 높아져 &lt;strong&gt;비계가 통째로 넘어진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이동식비계의 준수사항 (규칙 제68조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;준수사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바퀴에 브레이크·쐐기 등으로 갑작스러운 이동을 막고, 아웃트리거를 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강용 사다리는 견고하게 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계의 최상부에서 작업할 때는 안전난간을 설치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판 위에서 안전난간을 딛고 작업하거나 받침대·사다리를 사용하지 말 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「사용할 것」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판의 최대적재하중은 250 [kg]을 초과하지 말 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH114" s="32" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="AH115" s="32" t="inlineStr">
         <is>
-          <t>① 150 [kg] 이라는 기준은 없다.&lt;br&gt;② 200 [kg] 도 아니다.&lt;br&gt;④ 300 [kg] 도 아니다.</t>
+          <t>① 150 [kg]이라는 기준은 없다.&lt;br&gt;② 200 [kg] 도 아니다.&lt;br&gt;④ 300 [kg] 도 아니다.</t>
         </is>
       </c>
       <c r="AI115" s="32" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="AG116" s="32" t="inlineStr">
         <is>
-          <t>기둥 중심의 허용오차는 &lt;strong&gt;5 [mm]&lt;/strong&gt;다. 3 [mm] 가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;앵커볼트 매립의 허용오차&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;허용오차&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기둥 중심 — 기준선 및 인접기둥 중심에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [mm] 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앵커볼트 — 기둥 중심에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;베이스플레이트 하단 — 기준 높이 및 인접기둥 높이에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>기둥 중심의 허용오차는 &lt;strong&gt;5 [mm]&lt;/strong&gt;다. 3 [mm]가 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;앵커볼트 매립의 허용오차&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;허용오차&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기둥 중심 — 기준선 및 인접기둥 중심에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [mm]가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;앵커볼트 — 기둥 중심에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;베이스플레이트 하단 — 기준 높이 및 인접기둥 높이에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3 [mm] 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH116" s="32" t="inlineStr">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AH117" s="32" t="inlineStr">
         <is>
-          <t>① 강우량은 시간당 5 [mm] 가 아니라 1 [mm] 이상이다.&lt;br&gt;② 10 [mm] 도 아니다.&lt;br&gt;④ 강설량은 시간당 20 [mm] 가 아니라 1 [cm] 이상이다.</t>
+          <t>① 강우량은 시간당 5 [mm]가 아니라 1 [mm] 이상이다.&lt;br&gt;② 10 [mm] 도 아니다.&lt;br&gt;④ 강설량은 시간당 20 [mm]가 아니라 1 [cm] 이상이다.</t>
         </is>
       </c>
       <c r="AI117" s="32" t="inlineStr">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AG119" s="32" t="inlineStr">
         <is>
-          <t>설치각도는 &lt;strong&gt;수평면에서 60° 이내&lt;/strong&gt;이고, 지지점은 &lt;strong&gt;4개소 이상&lt;/strong&gt; 이라야 한다. 두 군데가 다 뒤집혔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;타워크레인의 와이어로프 지지 (규칙 제142조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;와이어로프를 고정하기 위한 전용 지지프레임을 사용할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치각도는 수평면에서 60° 이내로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「60° 이상」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지지점은 4개소 이상으로 하고 같은 각도로 배치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「4개소 미만」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;와이어로프와 그 고정부위는 충분한 강도와 장력을 갖도록 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;와이어로프가 가공전선에 근접하지 않도록 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>설치각도는 &lt;strong&gt;수평면에서 60° 이내&lt;/strong&gt;이고, 지지점은 &lt;strong&gt;4개소 이상&lt;/strong&gt;이라야 한다. 두 군데가 다 뒤집혔다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;타워크레인의 와이어로프 지지 (규칙 제142조)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;와이어로프를 고정하기 위한 전용 지지프레임을 사용할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치각도는 수평면에서 60° 이내로 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「60° 이상」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지지점은 4개소 이상으로 하고 같은 각도로 배치할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「4개소 미만」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;와이어로프와 그 고정부위는 충분한 강도와 장력을 갖도록 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;와이어로프가 가공전선에 근접하지 않도록 할 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH119" s="32" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="AI120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가공전선로 부근의 건설장비 작업&lt;/strong&gt;&lt;br&gt;세 대책이 모두 &lt;strong&gt;전선에서 멀리 떨어져 있게&lt;/strong&gt; 한다. 보기 ④는 &lt;strong&gt;아예 그 아래에 두겠다&lt;/strong&gt;는 것이라 정반대다. &lt;strong&gt;22.9 [kV] 는 접근한계거리 90 [cm]&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전선로 밑에 두지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가공전선로 부근의 건설장비 작업&lt;/strong&gt;&lt;br&gt;세 대책이 모두 &lt;strong&gt;전선에서 멀리 떨어져 있게&lt;/strong&gt; 한다. 보기 ④는 &lt;strong&gt;아예 그 아래에 두겠다&lt;/strong&gt;는 것이라 정반대다. &lt;strong&gt;22.9 [kV]는 접근한계거리 90 [cm]&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전선로 밑에 두지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>① 40 [m] 라는 기준은 없다.&lt;br&gt;③ 60 [m] 도 아니다.&lt;br&gt;④ 70 [m] 도 아니다.</t>
+          <t>① 40 [m]라는 기준은 없다.&lt;br&gt;③ 60 [m] 도 아니다.&lt;br&gt;④ 70 [m] 도 아니다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="AG122" s="32" t="inlineStr">
         <is>
-          <t>거꾸로다. &lt;strong&gt;경사로와 연약지반에서는 무한궤도식이 더 안전&lt;/strong&gt; 하다. &lt;strong&gt;접지면적이 넓어 덜 빠지고 덜 미끄러진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;무한궤도식과 타이어식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무한궤도식(크롤러)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;타이어식(휠)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;접지압&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮다(넓게 닿는다)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;연약지반·경사로&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안정적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠지거나 미끄러지기 쉽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;이동 속도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느리다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠르다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;도로 주행&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어렵다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쉽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>거꾸로다. &lt;strong&gt;경사로와 연약지반에서는 무한궤도식이 더 안전&lt;/strong&gt;하다. &lt;strong&gt;접지면적이 넓어 덜 빠지고 덜 미끄러진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;무한궤도식과 타이어식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무한궤도식(크롤러)&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;타이어식(휠)&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;접지압&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮다(넓게 닿는다)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;연약지반·경사로&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안정적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠지거나 미끄러지기 쉽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;이동 속도&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;느리다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빠르다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;도로 주행&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;어렵다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;쉽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH122" s="32" t="inlineStr">
